--- a/per-stock/PPL/financials.xlsx
+++ b/per-stock/PPL/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26241980416</v>
+        <v>26618155008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45293981696</v>
+        <v>45670154240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.398773</v>
+        <v>21.705523</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.477081</v>
+        <v>16.713278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.818082</v>
+        <v>2.8584788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1615124992</v>
+        <v>-1622000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>34.88</v>
+        <v>35.38</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D50</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C50</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B50</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B46:E46)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D48</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C48</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B48</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B44:E44)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D39</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C39</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B39</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B38:E38)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B5:E5)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1832,7 +2312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1858,32 +2338,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>2024-09-30</t>
         </is>
       </c>
     </row>
@@ -1894,19 +2374,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>4632000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>4347560.97561</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>4623115.577889</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>4086956.521739</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>3162790.697674</v>
-      </c>
       <c r="F2" s="3" t="n">
-        <v>2166666.666667</v>
+        <v>3168000</v>
       </c>
       <c r="G2" s="3" t="n"/>
     </row>
@@ -1917,19 +2397,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.189024</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.201005</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.204348</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0.197674</v>
-      </c>
       <c r="F3" s="3" t="n">
-        <v>0.180556</v>
+        <v>0.198</v>
       </c>
       <c r="G3" s="3" t="n"/>
     </row>
@@ -1940,19 +2420,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>1149000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>880000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>940000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>762000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>1032000000</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>732000000</v>
       </c>
       <c r="G4" s="3" t="n"/>
     </row>
@@ -1963,19 +2443,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>23000000</v>
+        <v>24000000</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>23000000</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>20000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>16000000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>12000000</v>
       </c>
       <c r="G5" s="3" t="n"/>
     </row>
@@ -1986,19 +2466,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>23000000</v>
+        <v>24000000</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>23000000</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>20000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>16000000</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>12000000</v>
       </c>
       <c r="G6" s="3" t="n"/>
     </row>
@@ -2009,19 +2489,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>452000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>266000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>318000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>183000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>414000000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>177000000</v>
       </c>
       <c r="G7" s="3" t="n"/>
     </row>
@@ -2032,19 +2512,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>389000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>366000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>355000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>353000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>342000000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>339000000</v>
       </c>
       <c r="G8" s="3" t="n"/>
     </row>
@@ -2055,19 +2535,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>1518000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>1323000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>1215000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>1165000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>1371000000</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>1392000000</v>
       </c>
       <c r="G9" s="3" t="n"/>
     </row>
@@ -2078,19 +2558,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>1173000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>903000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>963000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>782000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>1048000000</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>744000000</v>
       </c>
       <c r="G10" s="3" t="n"/>
     </row>
@@ -2101,19 +2581,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>784000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>537000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>608000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>429000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>706000000</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>405000000</v>
       </c>
       <c r="G11" s="3" t="n"/>
     </row>
@@ -2124,19 +2604,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-215000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-202000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-204000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-197000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-185000000</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>-181000000</v>
       </c>
       <c r="G12" s="3" t="n"/>
     </row>
@@ -2147,19 +2627,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>224000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>209000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>210000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>199000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>190000000</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>189000000</v>
       </c>
       <c r="G13" s="3" t="n"/>
     </row>
@@ -2170,19 +2650,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>6000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>5000000</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>8000000</v>
       </c>
       <c r="G14" s="3" t="n"/>
     </row>
@@ -2193,19 +2673,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>432632000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>247347560.97561</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>299623115.577889</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>167086956.521739</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>401162790.697674</v>
-      </c>
       <c r="F15" s="3" t="n">
-        <v>167166666.666667</v>
+        <v>401168000</v>
       </c>
       <c r="G15" s="3" t="n"/>
     </row>
@@ -2216,19 +2696,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>452000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>266000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>318000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>183000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>414000000</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>177000000</v>
       </c>
       <c r="G16" s="3" t="n"/>
     </row>
@@ -2239,19 +2719,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>2029000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>1798000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>1670000000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>1619000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>1826000000</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>1834000000</v>
       </c>
       <c r="G17" s="3" t="n"/>
     </row>
@@ -2262,19 +2742,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>745000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>476000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>569000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>406000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>678000000</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>377000000</v>
       </c>
       <c r="G18" s="3" t="n"/>
     </row>
@@ -2285,19 +2765,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>757158000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>745143000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>744290000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>742541000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>741400000</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>741063000</v>
       </c>
       <c r="G19" s="3" t="n"/>
     </row>
@@ -2308,19 +2788,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>751764000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>740113000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>739525000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>739276000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>738691000</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>737989000</v>
       </c>
       <c r="G20" s="3" t="n"/>
     </row>
@@ -2331,19 +2811,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0.36</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.43</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>0.5600000000000001</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>0.24</v>
       </c>
       <c r="G21" s="3" t="n"/>
     </row>
@@ -2354,19 +2834,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.36</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.43</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>0.5600000000000001</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>0.24</v>
       </c>
       <c r="G22" s="3" t="n"/>
     </row>
@@ -2377,19 +2857,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>451000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>266000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>318000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>183000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>413000000</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>177000000</v>
       </c>
       <c r="G23" s="3" t="n"/>
     </row>
@@ -2400,19 +2880,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>451000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>266000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>318000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>183000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>413000000</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>177000000</v>
       </c>
       <c r="G24" s="3" t="n"/>
     </row>
@@ -2423,20 +2903,20 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n">
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="G25" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>1000000</v>
       </c>
     </row>
     <row r="26">
@@ -2446,19 +2926,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>452000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>266000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>318000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>183000000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>414000000</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>177000000</v>
       </c>
       <c r="G26" s="3" t="n"/>
     </row>
@@ -2469,19 +2949,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>452000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>266000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>318000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>183000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>414000000</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>177000000</v>
       </c>
       <c r="G27" s="3" t="n"/>
     </row>
@@ -2492,19 +2972,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>452000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>266000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>318000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>183000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>414000000</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>177000000</v>
       </c>
       <c r="G28" s="3" t="n"/>
     </row>
@@ -2515,19 +2995,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>108000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>80000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>47000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>102000000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>39000000</v>
       </c>
       <c r="G29" s="3" t="n"/>
     </row>
@@ -2538,19 +3018,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>560000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>328000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>398000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>230000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>516000000</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>216000000</v>
       </c>
       <c r="G30" s="3" t="n"/>
     </row>
@@ -2561,19 +3041,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>54000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>33000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>21000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>23000000</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>20000000</v>
       </c>
       <c r="G31" s="3" t="n"/>
     </row>
@@ -2584,19 +3064,19 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>31000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>10000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>7000000</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>8000000</v>
       </c>
       <c r="G32" s="3" t="n"/>
     </row>
@@ -2607,19 +3087,19 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>23000000</v>
+        <v>24000000</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>23000000</v>
       </c>
       <c r="D33" s="3" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
         <v>20000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>16000000</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>12000000</v>
       </c>
       <c r="G33" s="3" t="n"/>
     </row>
@@ -2630,19 +3110,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-23000000</v>
+        <v>-24000000</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>-23000000</v>
       </c>
       <c r="D34" s="3" t="n">
+        <v>-23000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
         <v>-20000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-16000000</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>-12000000</v>
       </c>
       <c r="G34" s="3" t="n"/>
     </row>
@@ -2653,19 +3133,19 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-215000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-202000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-204000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-197000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-185000000</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>-181000000</v>
       </c>
       <c r="G35" s="3" t="n"/>
     </row>
@@ -2676,19 +3156,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>224000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>209000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>210000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>199000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>190000000</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>189000000</v>
       </c>
       <c r="G36" s="3" t="n"/>
     </row>
@@ -2699,19 +3179,19 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>6000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>5000000</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>8000000</v>
       </c>
       <c r="G37" s="3" t="n"/>
     </row>
@@ -2722,19 +3202,19 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>745000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>476000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>569000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>406000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>678000000</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>377000000</v>
       </c>
       <c r="G38" s="3" t="n"/>
     </row>
@@ -2745,19 +3225,19 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>473000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>444000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>431000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>425000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>435000000</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>425000000</v>
       </c>
       <c r="G39" s="3" t="n"/>
     </row>
@@ -2768,19 +3248,19 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>122000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>109000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>100000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>101000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>113000000</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>103000000</v>
       </c>
       <c r="G40" s="3" t="n"/>
     </row>
@@ -2791,16 +3271,16 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>351000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>335000000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>331000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>324000000</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>322000000</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>322000000</v>
@@ -2814,16 +3294,16 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>351000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>335000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>331000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>324000000</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>322000000</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>322000000</v>
@@ -2837,16 +3317,16 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>351000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>335000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>331000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>324000000</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>322000000</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>322000000</v>
@@ -2860,19 +3340,19 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>1218000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>920000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>1000000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>831000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>1113000000</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>802000000</v>
       </c>
       <c r="G44" s="3" t="n"/>
     </row>
@@ -2883,19 +3363,19 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>1556000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>1354000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>1239000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>1194000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>1391000000</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>1409000000</v>
       </c>
       <c r="G45" s="3" t="n"/>
     </row>
@@ -2906,19 +3386,19 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>2774000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>2274000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>2239000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>2025000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>2504000000</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>2211000000</v>
       </c>
       <c r="G46" s="3" t="n"/>
     </row>
@@ -2929,19 +3409,19 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>2774000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>2274000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>2239000000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>2025000000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>2504000000</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>2211000000</v>
       </c>
       <c r="G47" s="3" t="n"/>
     </row>
@@ -2950,7 +3430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4338,7 +4818,1651 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>18985000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>19937000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>31253000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>31295000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>31349000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>752178000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>751041000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>739545000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>739306000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>739066000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>771163000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>770978000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>770798000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>770601000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>770415000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>18997000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>18279000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>17884000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>17503000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>16973000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>20238000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>19350000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>18986000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>17797000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>17285000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>12446000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>12307000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>11854000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>11727000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>11738000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>35257000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>34231000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>33399000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>32083000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>31582000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-615000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-1059000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-2055000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-731000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>12446000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>12307000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>11854000000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>11727000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>11738000000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>15019000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>14881000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>14413000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>14286000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>14297000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>34043000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>32871000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>31349000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>29578000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>30235000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>15019000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>14881000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>14413000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>14286000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>14297000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>15019000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>14881000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>14413000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>14286000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>14297000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-200000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-202000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-193000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-190000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-184000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-200000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-202000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-193000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-190000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-184000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>548000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>575000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>901000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>902000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>904000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>3443000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>3207000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>3143000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>3027000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>3047000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>12316000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>12443000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>12356000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>12343000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>12330000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>31285000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>30363000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>29526000000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>28077000000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>27512000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>26978000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>25817000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>24835000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>23099000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>23685000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>556000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>480000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>468000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>426000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>449000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>272000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>281000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>284000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>294000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>298000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>272000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>281000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>284000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>294000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>298000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>3731000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>3615000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>3684000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>3611000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>3532000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>3731000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>3615000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>3684000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>3611000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>3532000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>19024000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>17990000000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>16936000000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>15292000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>15938000000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>19024000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>17990000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>16936000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>15292000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>15938000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Provisions</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>112000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>133000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>141000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>141000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>4307000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>4546000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>4691000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>4978000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>3827000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1094000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>1044000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>887000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>846000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>819000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>1214000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>1360000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>2050000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>2505000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>1347000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>1214000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1360000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>2050000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>2505000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1347000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n">
+        <v>904000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>1455000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1219000000</v>
+      </c>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n">
+        <v>551000000</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Commercial Paper</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n">
+        <v>456000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>595000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1286000000</v>
+      </c>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n">
+        <v>303000000</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>1999000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>2142000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>1754000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>1627000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1661000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>195000000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>237000000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>152000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>224000000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>195000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>237000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>152000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>224000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>1755000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1947000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1517000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1475000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1437000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Dividends Payable</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>210000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>198000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>197000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>197000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>197000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>142000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>190000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>132000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>143000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>143000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>1403000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1559000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1188000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1135000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1097000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>46304000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>45244000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>43939000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>42363000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>41809000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>41983000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>41313000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>40307000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>39440000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>38713000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>573000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>515000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>537000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>470000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>463000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>2573000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>2574000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>2559000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>2559000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>2559000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>326000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>327000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>312000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>312000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>312000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>2247000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>2247000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>2247000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>2247000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>2247000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>36737000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>36132000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>35153000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>34356000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>33642000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>-10522000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>-10329000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>-10217000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-9983000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>-9781000000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>47259000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>46461000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>45370000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>44339000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>43423000000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>3688000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>3437000000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>3513000000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>3088000000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>2695000000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>91000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>71000000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>81000000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>4321000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>3931000000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>3632000000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>2923000000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>3096000000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>518000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>420000000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>395000000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>407000000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>190000000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>106000000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>145000000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>192000000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>223000000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>536000000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>551000000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>517000000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>504000000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>476000000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>1836000000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>1783000000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>1458000000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>1538000000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1678000000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>92000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>117000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>101000000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>122000000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>93000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>1331000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>1108000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>1002000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>998000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1208000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>-158000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>-133000000</v>
+      </c>
+      <c r="D64" s="3" t="n"/>
+      <c r="E64" s="3" t="n">
+        <v>-171000000</v>
+      </c>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="n">
+        <v>-147000000</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>-137000000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>1489000000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>1241000000</v>
+      </c>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n">
+        <v>1169000000</v>
+      </c>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n">
+        <v>1108000000</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>1076000000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>1241000000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>1071000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>1102000000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>294000000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>312000000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>1241000000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1071000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1102000000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>294000000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>312000000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5766,13 +7890,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5782,6 +7906,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5792,30 +7917,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -5828,21 +7958,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-501000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-614000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-179000000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-328000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-280000000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-349000000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5850,7 +7981,9 @@
           <t>Repayment Of Debt</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="3" t="n">
+        <v>-18000000</v>
+      </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
@@ -5858,6 +7991,9 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
         <v>603000000</v>
       </c>
     </row>
@@ -5871,10 +8007,10 @@
         <v>1150000000</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>1150000000</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1895000000</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -5883,6 +8019,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5891,21 +8028,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-1058000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-1162000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-1145000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-930000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-793000000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-860000000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5914,21 +8052,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>1251000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>1086000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>1119000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>318000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>340000000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>339000000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5937,21 +8076,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>1086000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>1119000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>318000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>340000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>339000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>583000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5960,21 +8100,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>-33000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>801000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>-22000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>-244000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5983,21 +8124,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>654000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>563000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>982000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>306000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>271000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>119000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6006,21 +8148,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>654000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>563000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>982000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>306000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>271000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>119000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6029,21 +8172,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-32000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-21000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-14000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>6000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6052,21 +8196,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-201000000</v>
+        <v>-202000000</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>-201000000</v>
       </c>
       <c r="D12" s="3" t="n">
+        <v>-201000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>-202000000</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>-190000000</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>-190000000</v>
       </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6075,21 +8220,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-201000000</v>
+        <v>-202000000</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>-201000000</v>
       </c>
       <c r="D13" s="3" t="n">
+        <v>-201000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
         <v>-202000000</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-190000000</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>-190000000</v>
       </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6098,21 +8244,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>896000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>395000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>1204000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>508000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>475000000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>303000000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6121,21 +8268,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-236000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-139000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-691000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>508000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>475000000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>303000000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6144,13 +8292,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>1132000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>534000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>1895000000</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
@@ -6159,6 +8307,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6166,7 +8315,9 @@
           <t>Long Term Debt Payments</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
+      <c r="B17" s="3" t="n">
+        <v>-18000000</v>
+      </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
@@ -6176,6 +8327,9 @@
       <c r="G17" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H17" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6187,10 +8341,10 @@
         <v>1150000000</v>
       </c>
       <c r="C18" s="3" t="n">
+        <v>1150000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>1895000000</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
@@ -6199,6 +8353,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6207,21 +8362,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-1046000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-1144000000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-1147000000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-930000000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-783000000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-874000000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6230,21 +8386,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-1046000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-1144000000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-1147000000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-930000000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-783000000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-874000000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6253,21 +8410,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>18000000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-2000000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>10000000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>-14000000</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6276,21 +8434,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-1058000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-1162000000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-1145000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-930000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-793000000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-860000000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6299,21 +8458,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>557000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>548000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>966000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>602000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>513000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>511000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6322,21 +8482,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>557000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>548000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>966000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>602000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>513000000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>511000000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6345,21 +8506,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-281000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-38000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>235000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>42000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-233000000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-19000000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6368,21 +8530,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-85000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>116000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>30000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>13000000</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>-1000000</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>-1000000</v>
       </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6391,21 +8554,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-55000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>163000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>82000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-119000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-13000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>105000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6414,21 +8578,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>49000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-42000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>85000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-72000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>67000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-71000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6437,21 +8602,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>49000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-42000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>85000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-72000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>67000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-71000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6460,21 +8626,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-104000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>205000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-3000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-47000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-80000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>176000000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6483,21 +8650,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-56000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>147000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-47000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-120000000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>195000000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6506,21 +8674,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-48000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>58000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-11000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>40000000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-19000000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6529,21 +8698,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-48000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>58000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-11000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>40000000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-19000000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6552,21 +8722,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-84000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>52000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>47000000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>31000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-87000000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>41000000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6575,21 +8746,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>19000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-31000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-10000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-24000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>37000000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>7000000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6598,21 +8770,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-76000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-338000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>86000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>141000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-169000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-171000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6621,21 +8794,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-221000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-135000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>19000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>186000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-277000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-5000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6644,258 +8818,287 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-118000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>-97000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="D38" s="3" t="n">
-        <v>-28000000</v>
-      </c>
       <c r="E38" s="3" t="n">
-        <v>-32000000</v>
+        <v>-9000000</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>-61000000</v>
+        <v>-51000000</v>
       </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Deferred Tax</t>
+          <t>Stock Based Compensation</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>73000000</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>66000000</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>38000000</v>
-      </c>
+        <v>23000000</v>
+      </c>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n">
-        <v>49000000</v>
+        <v>19000000</v>
       </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Deferred Income Tax</t>
+          <t>Deferred Tax</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>94000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>15000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>73000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>66000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>38000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>49000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
+          <t>Deferred Income Tax</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>366000000</v>
+        <v>94000000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>355000000</v>
+        <v>15000000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>353000000</v>
+        <v>73000000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>342000000</v>
+        <v>66000000</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>339000000</v>
+        <v>38000000</v>
       </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>389000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>366000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>355000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>353000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>342000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>339000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Amortization Cash Flow</t>
+          <t>Depreciation And Amortization</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>31000000</v>
+        <v>389000000</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>24000000</v>
+        <v>366000000</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>29000000</v>
+        <v>355000000</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>20000000</v>
+        <v>353000000</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>17000000</v>
+        <v>342000000</v>
       </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Amortization Of Intangibles</t>
+          <t>Amortization Cash Flow</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>31000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>24000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>29000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>20000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>17000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Amortization Of Intangibles</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>335000000</v>
+        <v>38000000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>331000000</v>
+        <v>31000000</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>324000000</v>
+        <v>24000000</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>322000000</v>
+        <v>29000000</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>322000000</v>
+        <v>20000000</v>
       </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Operating Gains Losses</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-13000000</v>
+        <v>351000000</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>-14000000</v>
+        <v>335000000</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>-14000000</v>
+        <v>331000000</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>-16000000</v>
+        <v>324000000</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>-20000000</v>
+        <v>322000000</v>
       </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pension And Employee Benefit Expense</t>
+          <t>Operating Gains Losses</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>-13000000</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>-14000000</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>-14000000</v>
       </c>
       <c r="E47" s="3" t="n">
+        <v>-14000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
         <v>-16000000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>-20000000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>Pension And Employee Benefit Expense</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>-13000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>-14000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>-14000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>-16000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n">
+      <c r="B49" s="3" t="n">
+        <v>452000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>266000000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>318000000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>183000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>414000000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>177000000</v>
-      </c>
-      <c r="G48" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
